--- a/templates/tpl_booking_mssnhsj6ni6f.xlsx
+++ b/templates/tpl_booking_mssnhsj6ni6f.xlsx
@@ -188,6 +188,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -727,7 +776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>25</v>
       </c>
@@ -802,9 +851,6 @@
       <c r="F28"/>
       <c r="G28"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25"/>
     <row r="32" ht="21.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>35</v>
@@ -843,5 +889,6 @@
     <mergeCell ref="A32:I32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/tpl_booking_mssnhsj6ni6f.xlsx
+++ b/templates/tpl_booking_mssnhsj6ni6f.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="44">
   <si>
     <t>FROM:{{pol}}</t>
   </si>
@@ -29,12 +29,7 @@
     <t>{{consignee.name}}</t>
   </si>
   <si>
-    <t xml:space="preserve">HINNAWI INT'L.GROUP S.A.L.
-ACHRAFYEH, SIOUFI,
-WATERMASTER BLDG,2ND
-FLOOR,
-BEIRUT,
-Lebanon</t>
+    <t>{{consignee.address}}</t>
   </si>
   <si>
     <t xml:space="preserve">深圳安海华南物流有限公司
@@ -77,7 +72,7 @@
     <t>（收货地）</t>
   </si>
   <si>
-    <t xml:space="preserve">The port of destination </t>
+    <t>Destination port</t>
   </si>
   <si>
     <t>{{invoiceNo}}</t>
@@ -89,7 +84,7 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">                      * Description of Goods</t>
+    <t>* Description of Goods</t>
   </si>
   <si>
     <t xml:space="preserve">* Gross Weight </t>
@@ -129,13 +124,44 @@
   </si>
   <si>
     <t>*TOTAL :  (       ) X20'GP,    (   ) X40'GP,    (     ) X40'HQ,(     ) X45'HQ,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       (      )Ocean freight Prepaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          (       )Ocean freight collect</t>
+  </si>
+  <si>
+    <t>运费预付</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         运费到付</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remarks:
+1.请(用英文)填完整以上托运单并回传我司, 内容务必正确.
+2.我司的付款制度为付款交单, 故请提早安排付费事宜, 以免因付款原因影响放单.
+3.请提供详细的发票抬头, 以便我司出具发票.
+4.未尽事宜, 请在双方合作中协议解决.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订舱托书注意事项:
+1) 产品内如有任何电池类附件也请及时告知。请提供相应文件,如果无任何告知，默认为不含油和电池
+2) EX-WORK 条款货物，请在托书上备注清楚
+3)对于任何化工品/危险品的瞒报造成的一切后果和责任，都由委托方承担。</t>
+  </si>
+  <si>
+    <t>*托运人签章:</t>
+  </si>
+  <si>
+    <t>日期(DATE):</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -145,6 +171,22 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
     </font>
   </fonts>
   <fills count="3">
@@ -170,9 +212,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,7 +579,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -607,7 +659,7 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B9"/>
@@ -727,6 +779,7 @@
       <c r="G19" t="s">
         <v>15</v>
       </c>
+      <c r="H19"/>
       <c r="I19" t="s">
         <v>16</v>
       </c>
@@ -864,8 +917,156 @@
       <c r="H32"/>
       <c r="I32"/>
     </row>
+    <row r="33" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+    </row>
+    <row r="34" ht="15.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+    </row>
+    <row r="35" ht="15.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="H35" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" ht="31" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" ht="17.2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" ht="7.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+    </row>
+    <row r="43" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+    </row>
+    <row r="46" ht="13.9" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="28">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A4:E7"/>
     <mergeCell ref="A9:E13"/>
@@ -876,6 +1077,7 @@
     <mergeCell ref="F13:I13"/>
     <mergeCell ref="A15:E18"/>
     <mergeCell ref="F18:I18"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="G20:I20"/>
@@ -887,6 +1089,12 @@
     <mergeCell ref="E26:G28"/>
     <mergeCell ref="H26:H27"/>
     <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:E34"/>
+    <mergeCell ref="F33:I34"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="A36:D46"/>
+    <mergeCell ref="E36:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>

--- a/templates/tpl_booking_mssnhsj6ni6f.xlsx
+++ b/templates/tpl_booking_mssnhsj6ni6f.xlsx
@@ -200,7 +200,7 @@
       <patternFill/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -208,23 +208,169 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium"/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,7 +741,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
       <c r="B1"/>
@@ -618,55 +764,76 @@
       <c r="H2"/>
       <c r="I2"/>
     </row>
-    <row r="3" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="3" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B4"/>
       <c r="C4"/>
       <c r="D4"/>
       <c r="E4"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="6"/>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
-    </row>
-    <row r="6" ht="21" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="6"/>
+      <c r="I5" s="7"/>
+    </row>
+    <row r="6" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
       <c r="E6"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="6"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
       <c r="E7"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="F7" s="6"/>
+      <c r="I7" s="7"/>
+    </row>
+    <row r="8" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="6"/>
+      <c r="I8" s="7"/>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="23" t="s">
         <v>4</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
       <c r="E9"/>
-      <c r="F9" t="s">
+      <c r="F9" s="24" t="s">
         <v>5</v>
       </c>
       <c r="G9"/>
@@ -679,7 +846,7 @@
       <c r="C10"/>
       <c r="D10"/>
       <c r="E10"/>
-      <c r="F10" t="s">
+      <c r="F10" s="24" t="s">
         <v>6</v>
       </c>
       <c r="G10"/>
@@ -692,7 +859,7 @@
       <c r="C11"/>
       <c r="D11"/>
       <c r="E11"/>
-      <c r="F11" t="s">
+      <c r="F11" s="24" t="s">
         <v>7</v>
       </c>
       <c r="G11"/>
@@ -705,7 +872,7 @@
       <c r="C12"/>
       <c r="D12"/>
       <c r="E12"/>
-      <c r="F12" t="s">
+      <c r="F12" s="24" t="s">
         <v>8</v>
       </c>
       <c r="G12"/>
@@ -718,43 +885,51 @@
       <c r="C13"/>
       <c r="D13"/>
       <c r="E13"/>
-      <c r="F13" t="s">
+      <c r="F13" s="25" t="s">
         <v>9</v>
       </c>
       <c r="G13"/>
       <c r="H13"/>
       <c r="I13"/>
     </row>
-    <row r="14" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+    <row r="14" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="E14" s="4"/>
+      <c r="F14" s="6"/>
+      <c r="I14" s="7"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="22" t="s">
         <v>3</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
       <c r="E15"/>
-      <c r="F15" t="s">
+      <c r="F15" s="6" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="I15" s="7"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
       <c r="E16"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
       <c r="E17"/>
+      <c r="F17" s="6"/>
+      <c r="I17" s="7"/>
     </row>
     <row r="18" ht="21.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18"/>
@@ -762,95 +937,118 @@
       <c r="C18"/>
       <c r="D18"/>
       <c r="E18"/>
+      <c r="F18" s="25"/>
       <c r="G18"/>
       <c r="H18"/>
       <c r="I18"/>
     </row>
-    <row r="19" ht="16.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
+    <row r="19" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="7"/>
       <c r="E19" t="s">
         <v>13</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19"/>
-      <c r="I19" t="s">
+      <c r="I19" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" ht="30.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
       <c r="B20"/>
       <c r="C20"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="25"/>
       <c r="F20"/>
+      <c r="G20" s="25"/>
       <c r="H20"/>
       <c r="I20"/>
     </row>
-    <row r="21" ht="21.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+    <row r="21" ht="21.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D21" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="22" ht="19" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="H21" s="3"/>
+      <c r="I21" s="4"/>
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="12"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="25"/>
       <c r="F22"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="26" t="s">
         <v>20</v>
       </c>
       <c r="C23"/>
-      <c r="D23" t="s">
+      <c r="D23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H23" t="s">
+      <c r="F23" s="3"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B24" t="s">
+    <row r="24" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="27" t="s">
         <v>25</v>
       </c>
       <c r="C24"/>
-      <c r="D24" t="s">
+      <c r="D24" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="H24" t="s">
+      <c r="F24" s="14"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" s="11" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="28"/>
       <c r="B25"/>
       <c r="C25"/>
-      <c r="D25" t="s">
+      <c r="D25" s="22" t="s">
         <v>30</v>
       </c>
       <c r="E25" t="s">
@@ -862,10 +1060,10 @@
       <c r="G25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" s="7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -874,12 +1072,13 @@
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
+      <c r="E26" s="24"/>
       <c r="F26"/>
       <c r="G26"/>
-      <c r="H26" t="s">
+      <c r="H26" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" s="7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -892,20 +1091,48 @@
       <c r="F27"/>
       <c r="G27"/>
       <c r="H27"/>
-      <c r="I27" t="s">
+      <c r="I27" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
+      <c r="D28" s="9"/>
       <c r="E28"/>
       <c r="F28"/>
       <c r="G28"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="7"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="6"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="7"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="6"/>
+      <c r="I31" s="7"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="A32" s="22" t="s">
         <v>35</v>
       </c>
       <c r="B32"/>
@@ -918,152 +1145,170 @@
       <c r="I32"/>
     </row>
     <row r="33" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3" t="s">
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="G33" s="3"/>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="I33" s="16"/>
     </row>
     <row r="34" ht="15.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="A34" s="16"/>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
     </row>
     <row r="35" ht="15.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+      <c r="A35" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="H35" s="4" t="s">
+      <c r="B35" s="17"/>
+      <c r="C35" s="17"/>
+      <c r="D35" s="17"/>
+      <c r="E35" s="17"/>
+      <c r="H35" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="I35" s="4"/>
-    </row>
-    <row r="36" ht="31" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="I35" s="17"/>
+    </row>
+    <row r="36" ht="31" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5" t="s">
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-    </row>
-    <row r="39" ht="17.2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-    </row>
-    <row r="42" ht="7.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6" t="s">
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="7"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="18"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" ht="17.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="7"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="7"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="18"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="11"/>
+    </row>
+    <row r="42" ht="7.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="7"/>
+    </row>
+    <row r="43" ht="13.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="19" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="44" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-    </row>
-    <row r="45" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-    </row>
-    <row r="46" ht="13.9" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="7" t="s">
+      <c r="I43" s="7"/>
+    </row>
+    <row r="44" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="I44" s="7"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="18"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="I45" s="7"/>
+    </row>
+    <row r="46" ht="13.9" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="18"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="18"/>
+      <c r="D46" s="18"/>
+      <c r="E46" s="18"/>
+      <c r="F46" s="18"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="20" t="s">
         <v>43</v>
       </c>
+      <c r="I46" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/templates/tpl_booking_mssnhsj6ni6f.xlsx
+++ b/templates/tpl_booking_mssnhsj6ni6f.xlsx
@@ -200,7 +200,7 @@
       <patternFill/>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -213,91 +213,102 @@
       <right style="medium"/>
       <top style="medium"/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top/>
       <bottom/>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top/>
       <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -306,14 +317,18 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
@@ -325,52 +340,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1"/>
+    <xf borderId="2" applyBorder="1"/>
+    <xf borderId="3" applyBorder="1"/>
+    <xf borderId="4" applyBorder="1"/>
+    <xf borderId="5" applyBorder="1"/>
+    <xf borderId="6" applyBorder="1"/>
+    <xf borderId="7" applyBorder="1"/>
+    <xf borderId="8" applyBorder="1"/>
+    <xf borderId="9" applyBorder="1"/>
+    <xf borderId="10" applyBorder="1"/>
+    <xf borderId="11" applyBorder="1"/>
+    <xf borderId="12" applyBorder="1"/>
+    <xf borderId="13" applyBorder="1"/>
+    <xf borderId="14" applyBorder="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="15" applyBorder="1"/>
+    <xf borderId="16" applyBorder="1"/>
+    <xf borderId="17" applyBorder="1"/>
+    <xf borderId="18" applyBorder="1"/>
+    <xf borderId="19" applyBorder="1"/>
+    <xf borderId="20" applyBorder="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1"/>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -741,20 +785,20 @@
   </cols>
   <sheetData>
     <row r="1" ht="10" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1"/>
-      <c r="C1"/>
-      <c r="D1"/>
-      <c r="E1"/>
-      <c r="F1"/>
-      <c r="G1"/>
-      <c r="H1"/>
-      <c r="I1"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="10"/>
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2"/>
+      <c r="A2" s="11"/>
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
@@ -762,293 +806,293 @@
       <c r="F2"/>
       <c r="G2"/>
       <c r="H2"/>
-      <c r="I2"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="15"/>
+      <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+    </row>
+    <row r="4" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="17"/>
+      <c r="I4" s="18"/>
+      <c r="A4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B4"/>
-      <c r="C4"/>
-      <c r="D4"/>
-      <c r="E4"/>
-      <c r="F4" s="6"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="15"/>
+    </row>
+    <row r="5" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="17"/>
+      <c r="I5" s="18"/>
+      <c r="A5" s="17"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
-      <c r="E5"/>
-      <c r="F5" s="6"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" ht="21" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6"/>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" ht="21" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="17"/>
+      <c r="I6" s="18"/>
+      <c r="A6" s="17"/>
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
-      <c r="E6"/>
-      <c r="F6" s="6"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" ht="34" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7"/>
-      <c r="B7"/>
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7" s="6"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="17"/>
+      <c r="I7" s="18"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" ht="16" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="17"/>
+      <c r="I8" s="18"/>
+      <c r="A8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="6"/>
-      <c r="I8" s="7"/>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B9"/>
-      <c r="C9"/>
-      <c r="D9"/>
-      <c r="E9"/>
-      <c r="F9" s="24" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="23" t="s">
         <v>5</v>
       </c>
       <c r="G9"/>
       <c r="H9"/>
-      <c r="I9"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10"/>
+      <c r="A10" s="17"/>
       <c r="B10"/>
       <c r="C10"/>
       <c r="D10"/>
-      <c r="E10"/>
-      <c r="F10" s="24" t="s">
+      <c r="E10" s="18"/>
+      <c r="F10" s="23" t="s">
         <v>6</v>
       </c>
       <c r="G10"/>
       <c r="H10"/>
-      <c r="I10"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" ht="23" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11"/>
+      <c r="A11" s="17"/>
       <c r="B11"/>
       <c r="C11"/>
       <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11" s="24" t="s">
+      <c r="E11" s="18"/>
+      <c r="F11" s="23" t="s">
         <v>7</v>
       </c>
       <c r="G11"/>
       <c r="H11"/>
-      <c r="I11"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12"/>
+      <c r="A12" s="17"/>
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12" s="24" t="s">
+      <c r="E12" s="18"/>
+      <c r="F12" s="23" t="s">
         <v>8</v>
       </c>
       <c r="G12"/>
       <c r="H12"/>
-      <c r="I12"/>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13"/>
-      <c r="B13"/>
-      <c r="C13"/>
-      <c r="D13"/>
-      <c r="E13"/>
-      <c r="F13" s="25" t="s">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="G13"/>
-      <c r="H13"/>
-      <c r="I13"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="21"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="E14" s="15"/>
+      <c r="F14" s="17"/>
+      <c r="I14" s="18"/>
+      <c r="A14" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="6"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I15" s="18"/>
+      <c r="A15" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B15"/>
-      <c r="C15"/>
-      <c r="D15"/>
-      <c r="E15"/>
-      <c r="F15" s="6" t="s">
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="17"/>
+      <c r="I16" s="18"/>
+      <c r="A16" s="17"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
-      <c r="E16"/>
-      <c r="F16" s="6"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17"/>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="17"/>
+      <c r="I17" s="18"/>
+      <c r="A17" s="17"/>
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
-      <c r="E17"/>
-      <c r="F17" s="6"/>
-      <c r="I17" s="7"/>
+      <c r="E17" s="18"/>
     </row>
     <row r="18" ht="21.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18"/>
-      <c r="B18"/>
-      <c r="C18"/>
-      <c r="D18"/>
-      <c r="E18"/>
-      <c r="F18" s="25"/>
-      <c r="G18"/>
-      <c r="H18"/>
-      <c r="I18"/>
-    </row>
-    <row r="19" ht="16.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3" t="s">
+      <c r="F18" s="24"/>
+      <c r="A18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="21"/>
+    </row>
+    <row r="19" ht="16.5" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="18"/>
+      <c r="B19" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="7"/>
       <c r="E19" t="s">
         <v>13</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="18" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19"/>
-      <c r="I19" s="7" t="s">
+      <c r="I19" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" ht="30.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="25"/>
-      <c r="F20"/>
-      <c r="G20" s="25"/>
-      <c r="H20"/>
-      <c r="I20"/>
-    </row>
-    <row r="21" ht="21.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="3" t="s">
+      <c r="A20" s="24"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" ht="21.75" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="C21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+      <c r="B21" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="E21" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="G21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="4"/>
-    </row>
-    <row r="22" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="25"/>
-      <c r="F22"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="26" t="s">
+    </row>
+    <row r="22" ht="19" customHeight="1" spans="5:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="19"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="24"/>
+      <c r="I22" s="18"/>
+      <c r="F22" s="21"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="17"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="15"/>
+      <c r="B23" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="C23"/>
-      <c r="D23" s="13" t="s">
+      <c r="C23" s="15"/>
+      <c r="D23" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="E23" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6"/>
-      <c r="B24" s="27" t="s">
+    <row r="24" ht="14.25" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="17"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="21"/>
+      <c r="B24" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="C24"/>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="18"/>
+      <c r="D24" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11" t="s">
+      <c r="H24" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
-      <c r="B25"/>
-      <c r="C25"/>
-      <c r="D25" s="22" t="s">
+      <c r="A25" s="13"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="16" t="s">
         <v>30</v>
       </c>
       <c r="E25" t="s">
@@ -1060,255 +1104,255 @@
       <c r="G25" t="s">
         <v>32</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H25" s="25" t="s">
         <v>33</v>
       </c>
-      <c r="I25" s="7" t="s">
+      <c r="I25" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="26" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26"/>
+      <c r="E26" s="23"/>
+      <c r="A26" s="17"/>
       <c r="B26"/>
       <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26" s="24"/>
+      <c r="D26" s="23"/>
       <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26" s="24" t="s">
+      <c r="G26" s="18"/>
+      <c r="H26" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="18" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27"/>
+      <c r="A27" s="17"/>
       <c r="B27"/>
       <c r="C27"/>
-      <c r="D27"/>
-      <c r="E27"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="17"/>
       <c r="F27"/>
-      <c r="G27"/>
-      <c r="H27"/>
-      <c r="I27" s="7" t="s">
+      <c r="G27" s="18"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28"/>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D28" s="23"/>
+      <c r="H28" s="23"/>
+      <c r="I28" s="18"/>
+      <c r="A28" s="17"/>
       <c r="B28"/>
       <c r="C28"/>
-      <c r="D28" s="9"/>
-      <c r="E28"/>
+      <c r="E28" s="17"/>
       <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="6"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="7"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="4"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="6"/>
-      <c r="I31" s="7"/>
+      <c r="G28" s="18"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="17"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="17"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="18"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="17"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="17"/>
+      <c r="I31" s="18"/>
     </row>
     <row r="32" ht="21.75" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="22" t="s">
+      <c r="A32" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="B32"/>
-      <c r="C32"/>
-      <c r="D32"/>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32"/>
-      <c r="H32"/>
-      <c r="I32"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="28"/>
     </row>
     <row r="33" ht="17" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="16"/>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
       <c r="F33" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="32"/>
     </row>
     <row r="34" ht="15.6" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="35"/>
     </row>
     <row r="35" ht="15.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="31" t="s">
+      <c r="A35" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="17"/>
-      <c r="H35" s="32" t="s">
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="38"/>
+      <c r="H35" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="I35" s="17"/>
-    </row>
-    <row r="36" ht="31" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="33" t="s">
+      <c r="I35" s="39"/>
+    </row>
+    <row r="36" ht="31" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="13"/>
+      <c r="I36" s="15"/>
+      <c r="A36" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="34" t="s">
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="4"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="18"/>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="18"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="7"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="18"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="7"/>
-    </row>
-    <row r="39" ht="17.2" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="7"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="18"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="11"/>
-    </row>
-    <row r="42" ht="7.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="18"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="7"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="19" t="s">
+      <c r="F36" s="41"/>
+      <c r="G36" s="43"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H37" s="17"/>
+      <c r="I37" s="18"/>
+      <c r="A37" s="44"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="45"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H38" s="17"/>
+      <c r="I38" s="18"/>
+      <c r="A38" s="44"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="45"/>
+    </row>
+    <row r="39" ht="17.2" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H39" s="17"/>
+      <c r="I39" s="18"/>
+      <c r="A39" s="44"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="45"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H40" s="17"/>
+      <c r="I40" s="18"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="45"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H41" s="19"/>
+      <c r="I41" s="21"/>
+      <c r="A41" s="44"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="45"/>
+    </row>
+    <row r="42" ht="7.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H42" s="13"/>
+      <c r="I42" s="18"/>
+      <c r="A42" s="44"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="45"/>
+    </row>
+    <row r="43" ht="13.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="18"/>
+      <c r="A43" s="44"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I43" s="7"/>
-    </row>
-    <row r="44" ht="16" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
-      <c r="G44" s="18"/>
-      <c r="I44" s="7"/>
-    </row>
-    <row r="45" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="18"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
-      <c r="G45" s="18"/>
-      <c r="I45" s="7"/>
-    </row>
-    <row r="46" ht="13.9" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="18"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
-      <c r="G46" s="18"/>
-      <c r="H46" s="20" t="s">
+    </row>
+    <row r="44" ht="16" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I44" s="18"/>
+      <c r="A44" s="44"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="45"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I45" s="18"/>
+      <c r="A45" s="44"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="45"/>
+    </row>
+    <row r="46" ht="13.9" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="21"/>
+      <c r="A46" s="46"/>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="48"/>
+      <c r="H46" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="I46" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="28">

--- a/templates/tpl_booking_mssnhsj6ni6f.xlsx
+++ b/templates/tpl_booking_mssnhsj6ni6f.xlsx
@@ -434,19 +434,14 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="1366237" cy="1308100"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -477,7 +472,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/templates/tpl_booking_mssnhsj6ni6f.xlsx
+++ b/templates/tpl_booking_mssnhsj6ni6f.xlsx
@@ -340,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -415,6 +415,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf applyBorder="1" numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1"/>
+    <xf borderId="9" applyBorder="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -819,8 +822,10 @@
     <row r="4" ht="16" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="F4" s="17"/>
       <c r="I4" s="18"/>
-      <c r="A4" s="16" t="s">
-        <v>2</v>
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{{shipper.address}}</t>
+        </is>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
